--- a/model_analysis/generic_qf_multiple_single_variable_analysis_electrons.xlsx
+++ b/model_analysis/generic_qf_multiple_single_variable_analysis_electrons.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20955" windowHeight="12975" activeTab="2"/>
+    <workbookView windowWidth="17830" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="Interant d electrons_max_change" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Interant electrons_max_change_Y'!$B$1:$B$740</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Interant d electrons_max_change'!$B$1:$B$740</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -2273,7 +2274,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2284,13 +2285,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2758,28 +2752,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2788,118 +2785,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3267,6 +3261,11 @@
   <sheetPr/>
   <dimension ref="A1:C740"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="71.5" customWidth="1"/>
+    <col min="2" max="2" width="42.875" customWidth="1"/>
+    <col min="3" max="3" width="30.375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -11409,6 +11408,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B740" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -11419,6 +11421,11 @@
   <sheetPr/>
   <dimension ref="A1:C740"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="71.5" customWidth="1"/>
+    <col min="2" max="2" width="45.375" customWidth="1"/>
+    <col min="3" max="3" width="30.375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -19561,7 +19568,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B740">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B740" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
